--- a/UTCUTS/A1_Outputs/reference_works/A-O_AR_Model_Base_Year_REF.xlsx
+++ b/UTCUTS/A1_Outputs/reference_works/A-O_AR_Model_Base_Year_REF.xlsx
@@ -4772,7 +4772,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D710DE2-09D0-4D9D-A24E-169A169E5FC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77C71E67-837C-45D7-B3B1-A4B4C800EF6F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
